--- a/public/exports-from-60/29189935.xlsx
+++ b/public/exports-from-60/29189935.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017365</t>
+          <t xml:space="preserve">200017418</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">

--- a/public/exports-from-60/29189935.xlsx
+++ b/public/exports-from-60/29189935.xlsx
@@ -12064,7 +12064,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025497</t>
+          <t xml:space="preserve">200025503</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025497</t>
+          <t xml:space="preserve">200025503</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">

--- a/public/exports-from-60/29189935.xlsx
+++ b/public/exports-from-60/29189935.xlsx
@@ -9364,7 +9364,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017418</t>
+          <t xml:space="preserve">200017365</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025503</t>
+          <t xml:space="preserve">200025497</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025503</t>
+          <t xml:space="preserve">200025497</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
